--- a/LubanConfig/MiniTemplate/Datas/__enums__.xlsx
+++ b/LubanConfig/MiniTemplate/Datas/__enums__.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28227"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace2\luban_examples\MiniTemplate\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\悠手好闲\铁头工作室\方块项目设计案\《冲王》数值_cursor\LubanConfig\MiniTemplate\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57E1AAA0-A88D-4E41-AC05-256E9DB382D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="36">
   <si>
     <t>##var</t>
   </si>
@@ -77,12 +76,63 @@
   </si>
   <si>
     <t>注释</t>
+  </si>
+  <si>
+    <t>ChestType</t>
+  </si>
+  <si>
+    <t>Green</t>
+  </si>
+  <si>
+    <t>绿卡</t>
+  </si>
+  <si>
+    <t>Blue</t>
+  </si>
+  <si>
+    <t>蓝卡</t>
+  </si>
+  <si>
+    <t>Purple</t>
+  </si>
+  <si>
+    <t>紫卡</t>
+  </si>
+  <si>
+    <t>Orange</t>
+  </si>
+  <si>
+    <t>橙卡</t>
+  </si>
+  <si>
+    <t>Red</t>
+  </si>
+  <si>
+    <t>红卡</t>
+  </si>
+  <si>
+    <t>Gold</t>
+  </si>
+  <si>
+    <t>金币</t>
+  </si>
+  <si>
+    <t>Gem</t>
+  </si>
+  <si>
+    <t>宝石</t>
+  </si>
+  <si>
+    <t>Energy</t>
+  </si>
+  <si>
+    <t>体力</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -428,8 +478,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:L11"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="19" customWidth="1"/>
@@ -529,6 +579,100 @@
       </c>
       <c r="L3" s="1"/>
     </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H4" t="s">
+        <v>20</v>
+      </c>
+      <c r="I4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H5" t="s">
+        <v>22</v>
+      </c>
+      <c r="I5" t="s">
+        <v>23</v>
+      </c>
+      <c r="J5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H6" t="s">
+        <v>24</v>
+      </c>
+      <c r="I6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H7" t="s">
+        <v>26</v>
+      </c>
+      <c r="I7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I8" t="s">
+        <v>29</v>
+      </c>
+      <c r="J8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H9" t="s">
+        <v>30</v>
+      </c>
+      <c r="I9" t="s">
+        <v>31</v>
+      </c>
+      <c r="J9">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H10" t="s">
+        <v>32</v>
+      </c>
+      <c r="I10" t="s">
+        <v>33</v>
+      </c>
+      <c r="J10">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H11" t="s">
+        <v>34</v>
+      </c>
+      <c r="I11" t="s">
+        <v>35</v>
+      </c>
+      <c r="J11">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>
